--- a/Craw_data/Begin.xlsx
+++ b/Craw_data/Begin.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CO_2026\TTS-DATA\Craw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2499C054-F48C-4774-9692-4EA61C7B3B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296D9965-274B-4625-B3C2-1443DE9D51F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18180" yWindow="0" windowWidth="7510" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5170" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>https://www.youtube.com/@visaothenhipodcast</t>
   </si>
@@ -73,6 +84,42 @@
   </si>
   <si>
     <t>http://youtube.com/@ĐầuXanhMỏHỗn</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@TNVlogs-Giaimalichsu</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@heu.56mm</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@thanhphohuetv</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@podcast25phut33</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@bhttv</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@HieuTheConsul_Official</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@thepodcastofthuan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@canthobaoptth</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@baovaptthquangtri</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@angiang24gio</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@BáovàPTTHLâmĐồng1</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@TruyềnhìnhQuảngNgãi</t>
   </si>
 </sst>
 </file>
@@ -401,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="83.36328125" customWidth="1"/>
@@ -485,6 +532,71 @@
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -505,6 +617,18 @@
     <hyperlink ref="A14" r:id="rId14" xr:uid="{123602B2-D16F-4607-95C0-60841D8CC928}"/>
     <hyperlink ref="A15" r:id="rId15" xr:uid="{F83E6CCD-3F05-422D-AB9A-B92A4086E445}"/>
     <hyperlink ref="A16" r:id="rId16" xr:uid="{3EF6AB45-03B1-4D2D-BB61-AB93597A69C4}"/>
+    <hyperlink ref="A17" r:id="rId17" xr:uid="{C57C7DC6-FEBC-4DAF-AE40-F9416F1BE453}"/>
+    <hyperlink ref="A18" r:id="rId18" xr:uid="{733AFE20-D1EA-45E1-8962-2D024E4F541A}"/>
+    <hyperlink ref="A19" r:id="rId19" xr:uid="{8B4FA3A5-9235-4B76-9B96-B574DDCEA069}"/>
+    <hyperlink ref="A20" r:id="rId20" xr:uid="{3AF65C88-0FEB-4CD9-B887-92B72E304198}"/>
+    <hyperlink ref="A21" r:id="rId21" xr:uid="{E05AFFEB-EB6D-4EF4-AB88-259A826D5D04}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{7F4E223C-0E2A-4E80-9AA0-97137C6ABDB9}"/>
+    <hyperlink ref="A25" r:id="rId23" xr:uid="{B36DEDEA-6990-40A7-B841-74437651CDEF}"/>
+    <hyperlink ref="A26" r:id="rId24" xr:uid="{8C37309C-E23D-43DC-8EAE-129109712FBB}"/>
+    <hyperlink ref="A27" r:id="rId25" xr:uid="{1F2D6E84-8F50-4BE8-9EC1-73FA46D2441C}"/>
+    <hyperlink ref="A28" r:id="rId26" xr:uid="{D149AF92-9D10-4603-A14A-11D35C33B309}"/>
+    <hyperlink ref="A29" r:id="rId27" xr:uid="{B9B4140A-DB21-473C-8C4C-64CDD58C5494}"/>
+    <hyperlink ref="A24" r:id="rId28" xr:uid="{782DE413-FBDD-403E-9077-A79DF7960C82}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Craw_data/Begin.xlsx
+++ b/Craw_data/Begin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CO_2026\TTS-DATA\Craw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296D9965-274B-4625-B3C2-1443DE9D51F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724748BB-4DF2-49FF-A718-12550B1F4FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5170" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>https://www.youtube.com/@visaothenhipodcast</t>
   </si>
@@ -120,6 +120,27 @@
   </si>
   <si>
     <t>https://www.youtube.com/@TruyềnhìnhQuảngNgãi</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@TuanTienTi2911</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@MèoGiảiThích</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@vtv24</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@vietnamplus-w3i</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@hoainiem-kinhhong</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@TruyenDem-QStudio</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@kenhCoVan</t>
   </si>
 </sst>
 </file>
@@ -448,155 +469,195 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:A37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="83.36328125" customWidth="1"/>
+    <col min="1" max="1" width="83.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -629,6 +690,14 @@
     <hyperlink ref="A28" r:id="rId26" xr:uid="{D149AF92-9D10-4603-A14A-11D35C33B309}"/>
     <hyperlink ref="A29" r:id="rId27" xr:uid="{B9B4140A-DB21-473C-8C4C-64CDD58C5494}"/>
     <hyperlink ref="A24" r:id="rId28" xr:uid="{782DE413-FBDD-403E-9077-A79DF7960C82}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{3A8BED86-E952-4619-BC0D-949FFC83D34F}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{A72EC037-894E-4499-915A-21833C8B475D}"/>
+    <hyperlink ref="A32" r:id="rId31" xr:uid="{84145EB4-503A-4BBC-B5F4-AA12680F1B42}"/>
+    <hyperlink ref="A33" r:id="rId32" xr:uid="{78503CFD-A210-40A1-A32E-1DBF69954FCC}"/>
+    <hyperlink ref="A34" r:id="rId33" xr:uid="{FBEC8A15-FAE7-41D1-A06C-8A19AA6A25F8}"/>
+    <hyperlink ref="A35" r:id="rId34" xr:uid="{E30B944D-C752-4425-BC84-E4665C486326}"/>
+    <hyperlink ref="A36" r:id="rId35" xr:uid="{4A24A352-8F1D-468C-9E40-C69DBA6AB5DA}"/>
+    <hyperlink ref="A37" r:id="rId36" xr:uid="{F66A2622-86CD-4881-AFEA-96E34DE2E522}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Craw_data/Begin.xlsx
+++ b/Craw_data/Begin.xlsx
@@ -1,42 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CO_2026\TTS-DATA\Craw_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724748BB-4DF2-49FF-A718-12550B1F4FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="L/BxXHBMPZet1iH7vb7RiUzQOhJFun6bkjkpIr86zyY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>https://www.youtube.com/@visaothenhipodcast</t>
   </si>
@@ -50,6 +30,9 @@
     <t>https://www.youtube.com/@dunghobby</t>
   </si>
   <si>
+    <t>http://youtube.com/@ĐầuXanhMỏHỗn</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/@W2WMovie</t>
   </si>
   <si>
@@ -83,9 +66,6 @@
     <t>https://www.youtube.com/@ngthaithienphuc</t>
   </si>
   <si>
-    <t>http://youtube.com/@ĐầuXanhMỏHỗn</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/@TNVlogs-Giaimalichsu</t>
   </si>
   <si>
@@ -101,15 +81,15 @@
     <t>https://www.youtube.com/@bhttv</t>
   </si>
   <si>
+    <t>https://www.youtube.com/@canthobaoptth</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/@HieuTheConsul_Official</t>
   </si>
   <si>
     <t>https://www.youtube.com/@thepodcastofthuan</t>
   </si>
   <si>
-    <t>https://www.youtube.com/@canthobaoptth</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/@baovaptthquangtri</t>
   </si>
   <si>
@@ -141,27 +121,87 @@
   </si>
   <si>
     <t>https://www.youtube.com/@kenhCoVan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@spnsentai1135</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@MotSoiTranh</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@WeoBu</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@meokhongngheo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@kemberrr</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@taovangcomic6741</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@phaodaimotnguoi-1manfortress</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@W2WCartoon</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@PhêPhim</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@Diomio-Game</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@toilaTham</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@my_oasis</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@HeroKais4585</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@daylaphegame</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@gamecuchay</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@Nguoigiachoigamee</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@TheReviewerrrrr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -169,58 +209,56 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+  <cellXfs count="5">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="5B9BD5"/>
@@ -244,79 +282,19 @@
         <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -457,248 +435,1300 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="83.42578125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="83.43"/>
+    <col customWidth="1" min="2" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" xr:uid="{ACFE7D0B-7E28-4034-A3A2-47D84F223E8A}"/>
-    <hyperlink ref="A5" r:id="rId2" xr:uid="{481B545E-C360-4EB0-B390-067839549CE1}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{7221E44B-46C0-45CE-9021-21EB4EBDD797}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{B7B6A8D0-EC49-4B18-8690-5DE7B7921937}"/>
-    <hyperlink ref="A8" r:id="rId5" xr:uid="{9B625D07-537E-4AEB-A580-DAC8C751504E}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{B9B76FFB-96DB-4D2B-B817-2CC366D3BE50}"/>
-    <hyperlink ref="A9" r:id="rId7" xr:uid="{0F669B1C-467A-4933-AEF0-C2EBBE6ABF90}"/>
-    <hyperlink ref="A1" r:id="rId8" xr:uid="{E7C170C7-958D-46F2-AB5F-8880EF0EA69E}"/>
-    <hyperlink ref="A2" r:id="rId9" xr:uid="{7981D46A-3E93-40B0-8FCE-EF32AC1CDF49}"/>
-    <hyperlink ref="A10" r:id="rId10" xr:uid="{F0E0943F-05D6-406A-A067-FF387B9C6FCC}"/>
-    <hyperlink ref="A11" r:id="rId11" xr:uid="{6E51D545-1308-4FA7-8E0B-640D14879A68}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{0D6966A2-8BF1-45A6-A9C6-21C86B352042}"/>
-    <hyperlink ref="A12" r:id="rId13" xr:uid="{D16269C6-DAD0-4609-9AB8-3B270F75BB1C}"/>
-    <hyperlink ref="A14" r:id="rId14" xr:uid="{123602B2-D16F-4607-95C0-60841D8CC928}"/>
-    <hyperlink ref="A15" r:id="rId15" xr:uid="{F83E6CCD-3F05-422D-AB9A-B92A4086E445}"/>
-    <hyperlink ref="A16" r:id="rId16" xr:uid="{3EF6AB45-03B1-4D2D-BB61-AB93597A69C4}"/>
-    <hyperlink ref="A17" r:id="rId17" xr:uid="{C57C7DC6-FEBC-4DAF-AE40-F9416F1BE453}"/>
-    <hyperlink ref="A18" r:id="rId18" xr:uid="{733AFE20-D1EA-45E1-8962-2D024E4F541A}"/>
-    <hyperlink ref="A19" r:id="rId19" xr:uid="{8B4FA3A5-9235-4B76-9B96-B574DDCEA069}"/>
-    <hyperlink ref="A20" r:id="rId20" xr:uid="{3AF65C88-0FEB-4CD9-B887-92B72E304198}"/>
-    <hyperlink ref="A21" r:id="rId21" xr:uid="{E05AFFEB-EB6D-4EF4-AB88-259A826D5D04}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{7F4E223C-0E2A-4E80-9AA0-97137C6ABDB9}"/>
-    <hyperlink ref="A25" r:id="rId23" xr:uid="{B36DEDEA-6990-40A7-B841-74437651CDEF}"/>
-    <hyperlink ref="A26" r:id="rId24" xr:uid="{8C37309C-E23D-43DC-8EAE-129109712FBB}"/>
-    <hyperlink ref="A27" r:id="rId25" xr:uid="{1F2D6E84-8F50-4BE8-9EC1-73FA46D2441C}"/>
-    <hyperlink ref="A28" r:id="rId26" xr:uid="{D149AF92-9D10-4603-A14A-11D35C33B309}"/>
-    <hyperlink ref="A29" r:id="rId27" xr:uid="{B9B4140A-DB21-473C-8C4C-64CDD58C5494}"/>
-    <hyperlink ref="A24" r:id="rId28" xr:uid="{782DE413-FBDD-403E-9077-A79DF7960C82}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{3A8BED86-E952-4619-BC0D-949FFC83D34F}"/>
-    <hyperlink ref="A31" r:id="rId30" xr:uid="{A72EC037-894E-4499-915A-21833C8B475D}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{84145EB4-503A-4BBC-B5F4-AA12680F1B42}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{78503CFD-A210-40A1-A32E-1DBF69954FCC}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{FBEC8A15-FAE7-41D1-A06C-8A19AA6A25F8}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{E30B944D-C752-4425-BC84-E4665C486326}"/>
-    <hyperlink ref="A36" r:id="rId35" xr:uid="{4A24A352-8F1D-468C-9E40-C69DBA6AB5DA}"/>
-    <hyperlink ref="A37" r:id="rId36" xr:uid="{F66A2622-86CD-4881-AFEA-96E34DE2E522}"/>
+    <hyperlink r:id="rId1" ref="A1"/>
+    <hyperlink r:id="rId2" ref="A2"/>
+    <hyperlink r:id="rId3" ref="A3"/>
+    <hyperlink r:id="rId4" ref="A4"/>
+    <hyperlink r:id="rId5" ref="A5"/>
+    <hyperlink r:id="rId6" ref="A6"/>
+    <hyperlink r:id="rId7" ref="A7"/>
+    <hyperlink r:id="rId8" ref="A8"/>
+    <hyperlink r:id="rId9" ref="A9"/>
+    <hyperlink r:id="rId10" ref="A10"/>
+    <hyperlink r:id="rId11" ref="A11"/>
+    <hyperlink r:id="rId12" ref="A12"/>
+    <hyperlink r:id="rId13" ref="A13"/>
+    <hyperlink r:id="rId14" ref="A14"/>
+    <hyperlink r:id="rId15" ref="A15"/>
+    <hyperlink r:id="rId16" ref="A16"/>
+    <hyperlink r:id="rId17" ref="A17"/>
+    <hyperlink r:id="rId18" ref="A18"/>
+    <hyperlink r:id="rId19" ref="A19"/>
+    <hyperlink r:id="rId20" ref="A20"/>
+    <hyperlink r:id="rId21" ref="A21"/>
+    <hyperlink r:id="rId22" ref="A23"/>
+    <hyperlink r:id="rId23" ref="A24"/>
+    <hyperlink r:id="rId24" ref="A25"/>
+    <hyperlink r:id="rId25" ref="A26"/>
+    <hyperlink r:id="rId26" ref="A27"/>
+    <hyperlink r:id="rId27" ref="A28"/>
+    <hyperlink r:id="rId28" ref="A29"/>
+    <hyperlink r:id="rId29" ref="A30"/>
+    <hyperlink r:id="rId30" ref="A31"/>
+    <hyperlink r:id="rId31" ref="A32"/>
+    <hyperlink r:id="rId32" ref="A33"/>
+    <hyperlink r:id="rId33" ref="A34"/>
+    <hyperlink r:id="rId34" ref="A35"/>
+    <hyperlink r:id="rId35" ref="A36"/>
+    <hyperlink r:id="rId36" ref="A37"/>
+    <hyperlink r:id="rId37" ref="A38"/>
+    <hyperlink r:id="rId38" ref="A39"/>
+    <hyperlink r:id="rId39" ref="A40"/>
+    <hyperlink r:id="rId40" ref="A41"/>
+    <hyperlink r:id="rId41" ref="A42"/>
+    <hyperlink r:id="rId42" ref="A43"/>
+    <hyperlink r:id="rId43" ref="A44"/>
+    <hyperlink r:id="rId44" ref="A45"/>
+    <hyperlink r:id="rId45" ref="A46"/>
+    <hyperlink r:id="rId46" ref="A47"/>
+    <hyperlink r:id="rId47" ref="A48"/>
+    <hyperlink r:id="rId48" ref="A49"/>
+    <hyperlink r:id="rId49" ref="A50"/>
+    <hyperlink r:id="rId50" ref="A51"/>
+    <hyperlink r:id="rId51" ref="A52"/>
+    <hyperlink r:id="rId52" ref="A53"/>
+    <hyperlink r:id="rId53" ref="A54"/>
+    <hyperlink r:id="rId54" ref="A55"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId55"/>
 </worksheet>
 </file>